--- a/timetable-generator/Tables - Majors.xlsx
+++ b/timetable-generator/Tables - Majors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\ubuntu\home\eyad\timetable-generator\timetable-generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7FCDF1-80DC-41F8-997E-D96DF9AF4F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3A12A2-460F-479B-A320-FF1B52291929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19095" windowHeight="12075" xr2:uid="{150013C0-0388-42A9-86A1-272095128D9A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19095" windowHeight="12075" activeTab="1" xr2:uid="{150013C0-0388-42A9-86A1-272095128D9A}"/>
   </bookViews>
   <sheets>
     <sheet name="Courses" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="313">
   <si>
     <t>course_id</t>
   </si>
@@ -104,9 +104,6 @@
     <t>Lecture,Tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Japanese Culture </t>
-  </si>
-  <si>
     <t>LRA 101</t>
   </si>
   <si>
@@ -197,12 +194,6 @@
     <t>AID 321</t>
   </si>
   <si>
-    <t>AID 417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advanced Data Mining </t>
-  </si>
-  <si>
     <t>BIG Data Analytics &amp; Visualization</t>
   </si>
   <si>
@@ -299,9 +290,6 @@
     <t>Nada Essam</t>
   </si>
   <si>
-    <t>Adel Shakal</t>
-  </si>
-  <si>
     <t>Sherine Elmotasem</t>
   </si>
   <si>
@@ -380,9 +368,6 @@
     <t>ECE 324,ACM 215</t>
   </si>
   <si>
-    <t>Ayan w Mayet</t>
-  </si>
-  <si>
     <t>Ahmed Bayumi</t>
   </si>
   <si>
@@ -788,12 +773,6 @@
     <t>Software Security</t>
   </si>
   <si>
-    <t>Network Design and Management</t>
-  </si>
-  <si>
-    <t>CNC 415</t>
-  </si>
-  <si>
     <t>yyy</t>
   </si>
   <si>
@@ -845,9 +824,6 @@
     <t>CSC 410</t>
   </si>
   <si>
-    <t>CSC 412</t>
-  </si>
-  <si>
     <t>Software Verification and Validation (V&amp;V)</t>
   </si>
   <si>
@@ -896,9 +872,6 @@
     <t>BIF 425</t>
   </si>
   <si>
-    <t>BIF 424</t>
-  </si>
-  <si>
     <t>CSC 111, CSC 315,BIF 412</t>
   </si>
   <si>
@@ -980,7 +953,34 @@
     <t>CNC 413,CSC 415,BIF 424,CSC 412</t>
   </si>
   <si>
-    <t>test</t>
+    <t>Magles 4</t>
+  </si>
+  <si>
+    <t>Magles 5</t>
+  </si>
+  <si>
+    <t>Magles 6</t>
+  </si>
+  <si>
+    <t>Magles 7</t>
+  </si>
+  <si>
+    <t>Magles 8</t>
+  </si>
+  <si>
+    <t>Adel Ahmed</t>
+  </si>
+  <si>
+    <t>ggggg</t>
+  </si>
+  <si>
+    <t>kkk</t>
+  </si>
+  <si>
+    <t>test1</t>
+  </si>
+  <si>
+    <t>test2</t>
   </si>
 </sst>
 </file>
@@ -1105,8 +1105,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B11B111A-875C-434A-A14A-470BFFD88C56}" name="Table2" displayName="Table2" ref="A1:C52" totalsRowShown="0">
-  <autoFilter ref="A1:C52" xr:uid="{B11B111A-875C-434A-A14A-470BFFD88C56}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B11B111A-875C-434A-A14A-470BFFD88C56}" name="Table2" displayName="Table2" ref="A1:C47" totalsRowShown="0">
+  <autoFilter ref="A1:C47" xr:uid="{B11B111A-875C-434A-A14A-470BFFD88C56}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E444F8DC-8494-4078-9600-860DD0335B6E}" name="course_id"/>
     <tableColumn id="2" xr3:uid="{457389A4-9E93-4B8A-B891-E2A8E9FDA70B}" name="course_name"/>
@@ -1135,8 +1135,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{463FC2DC-13D2-41DA-93D7-9E07A593F1E0}" name="Table1" displayName="Table1" ref="A1:C47" totalsRowShown="0">
-  <autoFilter ref="A1:C47" xr:uid="{463FC2DC-13D2-41DA-93D7-9E07A593F1E0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{463FC2DC-13D2-41DA-93D7-9E07A593F1E0}" name="Table1" displayName="Table1" ref="A1:C52" totalsRowShown="0">
+  <autoFilter ref="A1:C52" xr:uid="{463FC2DC-13D2-41DA-93D7-9E07A593F1E0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C44">
     <sortCondition ref="A1:A44"/>
   </sortState>
@@ -1177,10 +1177,10 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{60260ED6-94B2-416C-98D7-C98D1144AAAD}" name="Table8" displayName="Table8" ref="A1:C54" totalsRowShown="0">
-  <autoFilter ref="A1:C54" xr:uid="{60260ED6-94B2-416C-98D7-C98D1144AAAD}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C54">
-    <sortCondition ref="A1:A54"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{60260ED6-94B2-416C-98D7-C98D1144AAAD}" name="Table8" displayName="Table8" ref="A1:C49" totalsRowShown="0">
+  <autoFilter ref="A1:C49" xr:uid="{60260ED6-94B2-416C-98D7-C98D1144AAAD}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C49">
+    <sortCondition ref="A1:A49"/>
   </sortState>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{179FECCB-5EF1-4E63-B57B-3C7EC99F7DFF}" name="year"/>
@@ -1488,7 +1488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECAC10A2-0620-4AD0-AC86-CF3FB68295CE}">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.19921875" customWidth="1"/>
@@ -1578,95 +1578,95 @@
         <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>211</v>
-      </c>
-      <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" t="s">
         <v>30</v>
       </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
         <v>32</v>
       </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" t="s">
         <v>34</v>
       </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" t="s">
         <v>36</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
@@ -1676,8 +1676,8 @@
       <c r="A17" t="s">
         <v>38</v>
       </c>
-      <c r="B17" t="s">
-        <v>37</v>
+      <c r="B17" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
@@ -1685,9 +1685,9 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s">
         <v>40</v>
       </c>
       <c r="C18" t="s">
@@ -1696,32 +1696,32 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" t="s">
         <v>42</v>
       </c>
-      <c r="B19" t="s">
-        <v>41</v>
-      </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B20" t="s">
-        <v>43</v>
-      </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
@@ -1729,21 +1729,21 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" t="s">
         <v>50</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="C23" t="s">
         <v>16</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>52</v>
@@ -1762,21 +1762,21 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" t="s">
         <v>54</v>
       </c>
-      <c r="B25" t="s">
-        <v>53</v>
-      </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
+      </c>
+      <c r="B26" t="s">
+        <v>57</v>
       </c>
       <c r="C26" t="s">
         <v>16</v>
@@ -1784,32 +1784,32 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>207</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>209</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>221</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>222</v>
       </c>
       <c r="C29" t="s">
         <v>16</v>
@@ -1817,32 +1817,32 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>212</v>
-      </c>
-      <c r="B30" t="s">
-        <v>214</v>
+        <v>225</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B31" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C31" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
+        <v>229</v>
+      </c>
+      <c r="B32" t="s">
         <v>230</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="C32" t="s">
         <v>16</v>
@@ -1850,21 +1850,21 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B33" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B34" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C34" t="s">
         <v>16</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
+        <v>239</v>
+      </c>
+      <c r="B35" t="s">
         <v>240</v>
-      </c>
-      <c r="B35" t="s">
-        <v>241</v>
       </c>
       <c r="C35" t="s">
         <v>16</v>
@@ -1883,10 +1883,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
+        <v>241</v>
+      </c>
+      <c r="B36" t="s">
         <v>242</v>
-      </c>
-      <c r="B36" t="s">
-        <v>243</v>
       </c>
       <c r="C36" t="s">
         <v>16</v>
@@ -1894,10 +1894,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="B37" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="C37" t="s">
         <v>16</v>
@@ -1905,10 +1905,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="B38" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C38" t="s">
         <v>16</v>
@@ -1916,10 +1916,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="B39" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C39" t="s">
         <v>16</v>
@@ -1927,10 +1927,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
+        <v>261</v>
+      </c>
+      <c r="B40" t="s">
         <v>260</v>
-      </c>
-      <c r="B40" t="s">
-        <v>261</v>
       </c>
       <c r="C40" t="s">
         <v>16</v>
@@ -1938,10 +1938,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B41" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C41" t="s">
         <v>16</v>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B42" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C42" t="s">
         <v>16</v>
@@ -1960,10 +1960,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B43" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="C43" t="s">
         <v>16</v>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B44" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C44" t="s">
         <v>16</v>
@@ -1982,90 +1982,35 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="B45" t="s">
-        <v>277</v>
+        <v>54</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="B46" t="s">
-        <v>279</v>
+        <v>54</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="B47" t="s">
-        <v>280</v>
+        <v>54</v>
       </c>
       <c r="C47" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
-        <v>283</v>
-      </c>
-      <c r="B48" t="s">
-        <v>282</v>
-      </c>
-      <c r="C48" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
-        <v>284</v>
-      </c>
-      <c r="B49" t="s">
-        <v>245</v>
-      </c>
-      <c r="C49" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
-        <v>307</v>
-      </c>
-      <c r="B50" t="s">
-        <v>57</v>
-      </c>
-      <c r="C50" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A51" t="s">
-        <v>308</v>
-      </c>
-      <c r="B51" t="s">
-        <v>57</v>
-      </c>
-      <c r="C51" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A52" t="s">
-        <v>309</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2089,16 +2034,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" t="s">
         <v>64</v>
-      </c>
-      <c r="B1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
@@ -2107,13 +2052,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
@@ -2122,10 +2067,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -2137,13 +2082,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>308</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
@@ -2152,13 +2097,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
@@ -2167,10 +2112,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -2182,13 +2127,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
@@ -2197,13 +2142,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
@@ -2212,13 +2157,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
@@ -2227,13 +2172,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
@@ -2242,13 +2187,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>112</v>
+        <v>309</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
@@ -2257,13 +2202,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
@@ -2272,13 +2217,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
@@ -2287,13 +2232,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
@@ -2302,13 +2247,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
@@ -2317,10 +2262,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -2332,13 +2277,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
@@ -2347,13 +2292,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
@@ -2362,13 +2307,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
@@ -2377,13 +2322,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
@@ -2392,13 +2337,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
@@ -2407,13 +2352,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
@@ -2422,13 +2367,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
@@ -2437,13 +2382,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
@@ -2452,13 +2397,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
@@ -2467,13 +2412,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
@@ -2482,13 +2427,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
@@ -2497,13 +2442,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D28" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
@@ -2512,13 +2457,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
@@ -2527,13 +2472,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D30" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
@@ -2542,13 +2487,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
@@ -2557,13 +2502,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
@@ -2572,13 +2517,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.45">
@@ -2587,13 +2532,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D34" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.45">
@@ -2602,13 +2547,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D35" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
@@ -2617,13 +2562,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C36" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D36" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
@@ -2632,13 +2577,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C37" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D37" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.45">
@@ -2647,13 +2592,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
@@ -2662,13 +2607,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D39" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
@@ -2677,13 +2622,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C40" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D40" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
@@ -2692,13 +2637,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C41" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D41" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
@@ -2707,13 +2652,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C42" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D42" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
@@ -2722,13 +2667,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C43" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D43" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.45">
@@ -2737,13 +2682,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C44" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D44" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
@@ -2752,13 +2697,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C45" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D45" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
@@ -2767,13 +2712,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C46" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D46" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.45">
@@ -2782,13 +2727,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C47" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.45">
@@ -2797,13 +2742,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
+        <v>123</v>
+      </c>
+      <c r="C48" t="s">
+        <v>73</v>
+      </c>
+      <c r="D48" t="s">
         <v>128</v>
-      </c>
-      <c r="C48" t="s">
-        <v>76</v>
-      </c>
-      <c r="D48" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
@@ -2812,13 +2757,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C49" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D49" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.45">
@@ -2827,13 +2772,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C50" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D50" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.45">
@@ -2842,13 +2787,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C51" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D51" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.45">
@@ -2857,13 +2802,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C52" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D52" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.45">
@@ -2872,13 +2817,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C53" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D53" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.45">
@@ -2887,13 +2832,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C54" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D54" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
@@ -2902,13 +2847,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C55" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D55" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.45">
@@ -2917,13 +2862,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="C56" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D56" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.45">
@@ -2932,13 +2877,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="C57" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D57" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.45">
@@ -2947,13 +2892,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="C58" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D58" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.45">
@@ -2962,13 +2907,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C59" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D59" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.45">
@@ -2977,13 +2922,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="C60" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D60" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.45">
@@ -2992,13 +2937,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>249</v>
+        <v>310</v>
       </c>
       <c r="C61" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D61" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.45">
@@ -3007,13 +2952,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="C62" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D62" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.45">
@@ -3022,13 +2967,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="C63" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D63" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
@@ -3037,13 +2982,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C64" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D64" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.45">
@@ -3055,10 +3000,10 @@
         <v>312</v>
       </c>
       <c r="C65" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D65" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -3071,7 +3016,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D74D33-1FE0-4647-A041-3A11F9673EDB}">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19.19921875" customWidth="1"/>
@@ -3081,18 +3026,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -3103,7 +3048,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
@@ -3114,10 +3059,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C4">
         <v>15</v>
@@ -3125,7 +3070,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
@@ -3136,7 +3081,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -3147,7 +3092,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
@@ -3158,7 +3103,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
@@ -3169,7 +3114,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
@@ -3180,7 +3125,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
@@ -3191,10 +3136,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B11" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C11">
         <v>15</v>
@@ -3202,10 +3147,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B12" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C12">
         <v>45</v>
@@ -3213,10 +3158,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C13">
         <v>30</v>
@@ -3224,10 +3169,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C14">
         <v>15</v>
@@ -3235,10 +3180,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C15">
         <v>15</v>
@@ -3246,10 +3191,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B16" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C16">
         <v>30</v>
@@ -3257,7 +3202,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
@@ -3268,7 +3213,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
@@ -3279,7 +3224,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B19" t="s">
         <v>8</v>
@@ -3290,7 +3235,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B20" t="s">
         <v>4</v>
@@ -3301,7 +3246,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B21" t="s">
         <v>4</v>
@@ -3312,7 +3257,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B22" t="s">
         <v>4</v>
@@ -3323,7 +3268,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B23" t="s">
         <v>4</v>
@@ -3334,7 +3279,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B24" t="s">
         <v>4</v>
@@ -3345,7 +3290,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
@@ -3356,7 +3301,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B26" t="s">
         <v>4</v>
@@ -3367,7 +3312,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B27" t="s">
         <v>4</v>
@@ -3378,7 +3323,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B28" t="s">
         <v>8</v>
@@ -3389,7 +3334,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B29" t="s">
         <v>8</v>
@@ -3400,7 +3345,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
@@ -3411,7 +3356,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B31" t="s">
         <v>4</v>
@@ -3422,7 +3367,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
@@ -3433,10 +3378,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B33" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C33">
         <v>15</v>
@@ -3444,10 +3389,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B34" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C34">
         <v>15</v>
@@ -3455,10 +3400,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B35" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C35">
         <v>15</v>
@@ -3466,10 +3411,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B36" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C36">
         <v>15</v>
@@ -3477,7 +3422,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B37" t="s">
         <v>8</v>
@@ -3488,10 +3433,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C38">
         <v>45</v>
@@ -3499,10 +3444,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B39" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C39">
         <v>45</v>
@@ -3510,7 +3455,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B40" t="s">
         <v>8</v>
@@ -3521,7 +3466,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B41" t="s">
         <v>8</v>
@@ -3532,7 +3477,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B42" t="s">
         <v>8</v>
@@ -3543,7 +3488,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B43" t="s">
         <v>8</v>
@@ -3554,7 +3499,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B44" t="s">
         <v>8</v>
@@ -3565,7 +3510,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="B45" t="s">
         <v>4</v>
@@ -3576,10 +3521,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C46">
         <v>30</v>
@@ -3587,13 +3532,68 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
+        <v>295</v>
+      </c>
+      <c r="B47" t="s">
+        <v>137</v>
+      </c>
+      <c r="C47">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>303</v>
+      </c>
+      <c r="B48" t="s">
+        <v>137</v>
+      </c>
+      <c r="C48">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
         <v>304</v>
       </c>
-      <c r="B47" t="s">
-        <v>142</v>
-      </c>
-      <c r="C47">
-        <v>15</v>
+      <c r="B49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>305</v>
+      </c>
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>306</v>
+      </c>
+      <c r="B51" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>307</v>
+      </c>
+      <c r="B52" t="s">
+        <v>137</v>
+      </c>
+      <c r="C52">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3617,24 +3617,24 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C2" s="5">
         <v>0.375</v>
@@ -3645,10 +3645,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C3" s="5">
         <v>0.44791666666666669</v>
@@ -3659,10 +3659,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C4" s="5">
         <v>0.52083333333333337</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C5" s="5">
         <v>0.59375</v>
@@ -3687,10 +3687,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C6" s="5">
         <v>0.375</v>
@@ -3701,10 +3701,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C7" s="5">
         <v>0.44791666666666669</v>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C8" s="5">
         <v>0.52083333333333337</v>
@@ -3729,10 +3729,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C9" s="5">
         <v>0.59375</v>
@@ -3743,10 +3743,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C10" s="5">
         <v>0.375</v>
@@ -3757,10 +3757,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C11" s="5">
         <v>0.44791666666666669</v>
@@ -3771,10 +3771,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C12" s="5">
         <v>0.52083333333333337</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C13" s="5">
         <v>0.59375</v>
@@ -3799,10 +3799,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C14" s="5">
         <v>0.375</v>
@@ -3813,10 +3813,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C15" s="5">
         <v>0.44791666666666669</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C16" s="5">
         <v>0.52083333333333337</v>
@@ -3841,10 +3841,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C17" s="5">
         <v>0.59375</v>
@@ -3855,10 +3855,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C18" s="5">
         <v>0.375</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C19" s="5">
         <v>0.44791666666666669</v>
@@ -3883,10 +3883,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C20" s="5">
         <v>0.52083333333333337</v>
@@ -3897,10 +3897,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C21" s="5">
         <v>0.59375</v>
@@ -3931,19 +3931,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D1" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
@@ -3957,7 +3957,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E2" s="4">
         <v>15</v>
@@ -3974,7 +3974,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E3" s="4">
         <v>15</v>
@@ -3991,7 +3991,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E4" s="4">
         <v>15</v>
@@ -4008,7 +4008,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E5" s="4">
         <v>15</v>
@@ -4025,7 +4025,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E6" s="4">
         <v>15</v>
@@ -4042,7 +4042,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E7" s="4">
         <v>15</v>
@@ -4059,7 +4059,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E8" s="4">
         <v>15</v>
@@ -4076,7 +4076,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E9" s="4">
         <v>15</v>
@@ -4093,7 +4093,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E10" s="4">
         <v>15</v>
@@ -4110,7 +4110,7 @@
         <v>2</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E11" s="4">
         <v>15</v>
@@ -4127,7 +4127,7 @@
         <v>2</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E12" s="4">
         <v>15</v>
@@ -4144,7 +4144,7 @@
         <v>2</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E13" s="4">
         <v>15</v>
@@ -4161,7 +4161,7 @@
         <v>2</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E14" s="4">
         <v>15</v>
@@ -4178,7 +4178,7 @@
         <v>2</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E15" s="4">
         <v>15</v>
@@ -4195,7 +4195,7 @@
         <v>2</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E16" s="4">
         <v>15</v>
@@ -4212,7 +4212,7 @@
         <v>2</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E17" s="4">
         <v>15</v>
@@ -4229,7 +4229,7 @@
         <v>2</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E18" s="4">
         <v>15</v>
@@ -4246,7 +4246,7 @@
         <v>2</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E19" s="4">
         <v>15</v>
@@ -4263,7 +4263,7 @@
         <v>3</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E20" s="4">
         <v>15</v>
@@ -4280,7 +4280,7 @@
         <v>3</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E21" s="4">
         <v>15</v>
@@ -4297,7 +4297,7 @@
         <v>3</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E22" s="4">
         <v>15</v>
@@ -4314,7 +4314,7 @@
         <v>3</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E23" s="4">
         <v>15</v>
@@ -4331,7 +4331,7 @@
         <v>3</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E24" s="4">
         <v>15</v>
@@ -4348,7 +4348,7 @@
         <v>3</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E25" s="4">
         <v>15</v>
@@ -4365,7 +4365,7 @@
         <v>3</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E26" s="4">
         <v>15</v>
@@ -4382,7 +4382,7 @@
         <v>3</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E27" s="4">
         <v>15</v>
@@ -4399,7 +4399,7 @@
         <v>3</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E28" s="4">
         <v>15</v>
@@ -4416,7 +4416,7 @@
         <v>4</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E29" s="4">
         <v>15</v>
@@ -4433,7 +4433,7 @@
         <v>4</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E30" s="4">
         <v>15</v>
@@ -4450,7 +4450,7 @@
         <v>4</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E31" s="4">
         <v>15</v>
@@ -4467,7 +4467,7 @@
         <v>4</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E32" s="4">
         <v>15</v>
@@ -4484,7 +4484,7 @@
         <v>4</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E33" s="4">
         <v>15</v>
@@ -4501,7 +4501,7 @@
         <v>4</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E34" s="4">
         <v>15</v>
@@ -4518,7 +4518,7 @@
         <v>4</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E35" s="4">
         <v>15</v>
@@ -4535,7 +4535,7 @@
         <v>4</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E36" s="4">
         <v>15</v>
@@ -4552,7 +4552,7 @@
         <v>4</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E37" s="4">
         <v>15</v>
@@ -4568,7 +4568,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E3675F3-5241-4B74-A0FC-A9EE607E5844}">
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="18.1328125" customWidth="1"/>
@@ -4578,13 +4578,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
@@ -4595,7 +4595,7 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
@@ -4606,7 +4606,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
@@ -4614,10 +4614,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
@@ -4625,10 +4625,10 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>207</v>
       </c>
       <c r="C5" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
@@ -4636,10 +4636,10 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>212</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
@@ -4647,10 +4647,10 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
@@ -4658,21 +4658,21 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
@@ -4680,10 +4680,10 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
@@ -4691,10 +4691,10 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
@@ -4702,10 +4702,10 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
@@ -4713,10 +4713,10 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
@@ -4724,10 +4724,10 @@
         <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
@@ -4735,10 +4735,10 @@
         <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>206</v>
       </c>
       <c r="C15" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
@@ -4746,21 +4746,21 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
@@ -4768,10 +4768,10 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
@@ -4779,10 +4779,10 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>229</v>
       </c>
       <c r="C19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
@@ -4790,10 +4790,10 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>234</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
@@ -4801,10 +4801,10 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>221</v>
       </c>
       <c r="C21" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.45">
@@ -4812,10 +4812,10 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>226</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
@@ -4823,10 +4823,10 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>225</v>
       </c>
       <c r="C23" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.45">
@@ -4834,10 +4834,10 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C24" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.45">
@@ -4845,10 +4845,10 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>232</v>
+        <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.45">
@@ -4856,21 +4856,21 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>210</v>
       </c>
       <c r="C27" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.45">
@@ -4878,10 +4878,10 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>215</v>
+        <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.45">
@@ -4889,10 +4889,10 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C29" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.45">
@@ -4900,10 +4900,10 @@
         <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C30" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">
@@ -4914,7 +4914,7 @@
         <v>58</v>
       </c>
       <c r="C31" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
@@ -4922,10 +4922,10 @@
         <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
@@ -4933,10 +4933,10 @@
         <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>298</v>
       </c>
       <c r="C33" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.45">
@@ -4944,10 +4944,10 @@
         <v>4</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>270</v>
       </c>
       <c r="C34" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.45">
@@ -4955,10 +4955,10 @@
         <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>307</v>
+        <v>268</v>
       </c>
       <c r="C35" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.45">
@@ -4966,10 +4966,10 @@
         <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C36" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.45">
@@ -4977,10 +4977,10 @@
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C37" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.45">
@@ -4988,10 +4988,10 @@
         <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="C38" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.45">
@@ -4999,10 +4999,10 @@
         <v>4</v>
       </c>
       <c r="B39" t="s">
-        <v>284</v>
+        <v>237</v>
       </c>
       <c r="C39" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.45">
@@ -5010,10 +5010,10 @@
         <v>4</v>
       </c>
       <c r="B40" t="s">
-        <v>283</v>
+        <v>234</v>
       </c>
       <c r="C40" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.45">
@@ -5021,10 +5021,10 @@
         <v>4</v>
       </c>
       <c r="B41" t="s">
-        <v>244</v>
+        <v>300</v>
       </c>
       <c r="C41" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.45">
@@ -5032,10 +5032,10 @@
         <v>4</v>
       </c>
       <c r="B42" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C42" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.45">
@@ -5043,10 +5043,10 @@
         <v>4</v>
       </c>
       <c r="B43" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C43" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.45">
@@ -5054,10 +5054,10 @@
         <v>4</v>
       </c>
       <c r="B44" t="s">
-        <v>309</v>
+        <v>259</v>
       </c>
       <c r="C44" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.45">
@@ -5065,10 +5065,10 @@
         <v>4</v>
       </c>
       <c r="B45" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.45">
@@ -5076,10 +5076,10 @@
         <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>246</v>
+        <v>299</v>
       </c>
       <c r="C46" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.45">
@@ -5087,10 +5087,10 @@
         <v>4</v>
       </c>
       <c r="B47" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="C47" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.45">
@@ -5098,10 +5098,10 @@
         <v>4</v>
       </c>
       <c r="B48" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="C48" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.45">
@@ -5109,65 +5109,10 @@
         <v>4</v>
       </c>
       <c r="B49" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="C49" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A50">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>267</v>
-      </c>
-      <c r="C50" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A51">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>308</v>
-      </c>
-      <c r="C51" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A52">
-        <v>4</v>
-      </c>
-      <c r="B52" t="s">
-        <v>260</v>
-      </c>
-      <c r="C52" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>262</v>
-      </c>
-      <c r="C53" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>263</v>
-      </c>
-      <c r="C54" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/timetable-generator/Tables - Majors.xlsx
+++ b/timetable-generator/Tables - Majors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\ubuntu\home\eyad\timetable-generator\timetable-generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3A12A2-460F-479B-A320-FF1B52291929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C39870-0BE0-493D-8B52-4C5EC5B9F657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19095" windowHeight="12075" activeTab="1" xr2:uid="{150013C0-0388-42A9-86A1-272095128D9A}"/>
   </bookViews>
@@ -2160,7 +2160,7 @@
         <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
         <v>263</v>
